--- a/datos/Plan_Sectorial_Relevo_Generacional.xlsx
+++ b/datos/Plan_Sectorial_Relevo_Generacional.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u0899rpe\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3246CE55-C817-4347-A8F9-86BD6A460F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B22421B5-20A3-4240-9C84-76E3D0F6A140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="38596" windowHeight="21075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11235" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="331">
   <si>
     <t>Plan Sectorial — Estrategia de Relevo Generacional</t>
   </si>
@@ -1021,6 +1021,222 @@
   </si>
   <si>
     <t>5 sesiones de presentación del itinerario en Gipuzkoa (Ordizia, Elgoibar, Tolosa, Azpeitia, Hernani) con 66 personas (30M, 36H). Itinerario con 6 sesiones: 4 realizadas en 2025 con 29 personas (16M, 13H). En 2026: módulo PAC (21 personas) y programas de retirada (17 personas inscritas).</t>
+  </si>
+  <si>
+    <t>Euskal lehen sektorean profesional berriak sar daitezen sustatzeko zeharkako estrategia, urtean 125 gazte erakartzeko eta hurrengo hamarkadan 1.500 ustiategiren erreleboa errazteko.</t>
+  </si>
+  <si>
+    <t>Gazte berrien tasa</t>
+  </si>
+  <si>
+    <t>Belaunaldi-erreleboa duten ustiategien ehunekoa</t>
+  </si>
+  <si>
+    <t>Ustiategien titularren batez besteko adina</t>
+  </si>
+  <si>
+    <t>Gazteek kudeatutako nekazaritza-azalera erabilgarria (NAE)</t>
+  </si>
+  <si>
+    <t>Txanda-programetan onartutako eskaerak</t>
+  </si>
+  <si>
+    <t>Ustiategi berriak finkatzeko arrakasta-tasa</t>
+  </si>
+  <si>
+    <t>Txanda sustatzeko laguntzaren lagatzaile onuradunak</t>
+  </si>
+  <si>
+    <t>Finantzaketa eta laguntzak eskuratzea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestakuntzan eta aholkularitzan parte hartzea
+</t>
+  </si>
+  <si>
+    <t>Genero-dibertsifikazioa</t>
+  </si>
+  <si>
+    <t>Mentoretza- edo laguntza-programetan parte hartzen duten ustiategiak</t>
+  </si>
+  <si>
+    <t>Mentoretza- edo laguntza-programetan parte hartzen duten ustiategien kopurua (GAZTENEK, langile anitzekin, 40 urtetik gorakoak aholkularitzarekin, Nekazaritzako Test Guneak, Etorkizuna Bermatuz).</t>
+  </si>
+  <si>
+    <t>Nekazaritza-sektorean sartutako emakumeen ehunekoa, urteko laneratze guztiekiko. 1. adierazletik eratorritako datua, sexuaren arabera bereizita.</t>
+  </si>
+  <si>
+    <t>Lanean hasi aurretik prestakuntza espezifikoa jasotzen duten gazteen kopurua, lanean hasi diren gazte guztiekiko. Prestakuntza arautua (LH, batez bestekoa, unibertsitatekoa) eta arautu gabea bereiztea.</t>
+  </si>
+  <si>
+    <t>Txanda sustatzeko laguntza jasotzen duten lagatzaileen kopurua. Ikus 5.5.2 jarduera.</t>
+  </si>
+  <si>
+    <t>Instalaziorako finantza-laguntza jasotzen duten gazteen kopurua, langile guztien aldean. Iturriak: Sendotu, GAZTENEK, Baserritar Misto Profesionala, Nekazaritzako Test Espazioak, inbertsioetarako laguntzak.</t>
+  </si>
+  <si>
+    <t>3-5 urteren ondoren sektorean jarraitzen duten gazteak. GAZTENEK bidez (1. batzordetik 2. batzordera igarotzea) eta/edo jarraipen-deia, 2. batzordetik hiru urtera.</t>
+  </si>
+  <si>
+    <t>Belaunaldien arteko errelebo programetan onartutako eskaeren kopurua (GAZTENEK, Nekazaritzako Test Guneak, Hurbiltzeko Bekak, Egonaldi praktikoak eta laburrak, Baserritar Misto Profesionala, ordezkapen zerbitzuak, etab.).</t>
+  </si>
+  <si>
+    <t>Titular berriek kudeatutako hektareen hazkundea. Gazteek kudeatutako hektareak eta gazte bakoitzeko batez besteko azalera hartzen ditu.</t>
+  </si>
+  <si>
+    <t>Nekazaritzako titularren batez besteko adina pixkanaka murriztea Euskadin. Erreferentzia: 58,4 urte ustiategi guztientzat eta 54,0 urte profesionalentzat. 2030eko Nekazaritza Zentsuaren behin betiko datua.</t>
+  </si>
+  <si>
+    <t>Gazteak sartu dituzten Euskadiko nekazaritza-ustiategien proportzioa, belaunaldi-erreleboa behar duten ustiategi guztiekiko (764 erreleborik gabeko ustiategi, identifikatutako 1.482 guztira).</t>
+  </si>
+  <si>
+    <t>Nekazaritza-sektorean sartu diren langile berrien kopurua, urteka. Sexuaren arabera banakatzea gomendatzen da (GAZTENEK, 1. eta 2. batzordea, GFAko baserritar misto profesionala).</t>
+  </si>
+  <si>
+    <t>8/2014 EPJA Dekretuaren aldaketa</t>
+  </si>
+  <si>
+    <t>PEPAC – Nekazari aktiboa</t>
+  </si>
+  <si>
+    <t>Txanda sustatzeko laguntzen agindua</t>
+  </si>
+  <si>
+    <t>Herritarrak sentsibilizatzeko kanpaina</t>
+  </si>
+  <si>
+    <t>Gazteak sentsibilizatzeko kanpaina</t>
+  </si>
+  <si>
+    <t>Zerbitzu ekosistemikoen ebaluazioa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nekazaritzako testak egiteko guneak
+</t>
+  </si>
+  <si>
+    <t>Egonaldi praktikoak eta egonaldi laburrak</t>
+  </si>
+  <si>
+    <t>Gazteen hurbilketa bultzatzeko beste modu batzuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Txertatzeko gida
+</t>
+  </si>
+  <si>
+    <t>Bitartekaritza-bulegoak</t>
+  </si>
+  <si>
+    <t>GAZTENEK berrikustea</t>
+  </si>
+  <si>
+    <t>Txanda sustatzeko laguntza</t>
+  </si>
+  <si>
+    <t>Inbertsioetarako laguntzak hobetzea</t>
+  </si>
+  <si>
+    <t>Laguntza fiskalen azterketa</t>
+  </si>
+  <si>
+    <t>SENDOTU finantza-tresna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nekazaritza-eskoletako prestakuntza
+</t>
+  </si>
+  <si>
+    <t>Prestakuntza, digitalizazioa eta berrikuntza</t>
+  </si>
+  <si>
+    <t>Gazteak instalatzeko aholkularitza</t>
+  </si>
+  <si>
+    <t>Ustiategien balizko lagatzaileentzako prestakuntza espezializatua</t>
+  </si>
+  <si>
+    <t>Landa-zerbitzuak eta -ekipamenduak</t>
+  </si>
+  <si>
+    <t>Abeltzaintzako prestakuntza espezializaturako instalazioak eta programak hobetzea.</t>
+  </si>
+  <si>
+    <t>Gazteak teknologia berrietan, agritech-etan eta enpresa-kudeaketan trebatzea.</t>
+  </si>
+  <si>
+    <t>Maileguetarako abal-sistema bat sortzea, finantzaketa-oztopoak murriztuz.</t>
+  </si>
+  <si>
+    <t>Ustiategi gazte eta lagatzaileentzako kenkari fiskal berriak aztertzea.</t>
+  </si>
+  <si>
+    <t>Gazteen eta emakumeen inbertsioetarako laguntza ekonomikoak areagotzea.</t>
+  </si>
+  <si>
+    <t>Sektorean sartzeko bideak, laguntzak eta eskura dauden baliabideak zehazten dituen dokumentu bat sortzea.</t>
+  </si>
+  <si>
+    <t>Sektorearen ingurumen- eta gizarte-onurak kuantifikatzea, politika publikoei laguntzeko.</t>
+  </si>
+  <si>
+    <t>Gazteen talentua erakartzea, sektoreko errentagarritasuna eta bizi-kalitatea erakutsiz.</t>
+  </si>
+  <si>
+    <t>Nekazaritza-sektoreak gizarte-, kultura- eta ingurumen-eragile gisa duen pertzepzioa hobetzea.</t>
+  </si>
+  <si>
+    <t>Test-espazioetarako laguntzak arautuko dituen eta belaunaldien arteko erreleboa sustatuko duen arau espezifiko bat sortzea.</t>
+  </si>
+  <si>
+    <t>Nekazari aktiboaren kontzeptua aldatzea, NPBko baliabideak askatzeko eta gazteei bideratzeko.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nekazari Gazteen Estatutua eguneratzea, behar berrietara egokitzeko eta genero-berdintasuna sustatzeko.
+[Arduradunkidea (k): foru-aldundiak] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ustiategiak kudeatzeko aldi baterako esperientziak ematea, behin betiko sartu aurretik.
+[Arduradunkidea (k): foru-aldundiak] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokiko eta nazioarteko ustiategietan mugikortasuna eta ikaskuntza praktikoa sustatzea.
+[Arduradunkidea (k): EJ] 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordezkapen-zerbitzuetarako eta nekazaritza-laneko enpresetarako sarbidea hobetzea, gazteak sartzeko bide gisa.
+[Arduradunkidea (k): foru-aldundiak] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Txandarik gabeko ustiategiak sektorean sartu nahi duten gazteekin lotzea.
+[Arduradunkidea (k): foru-aldundiak] 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nekazari gazteentzako instalazio-prozedura sinplifikatzea eta hobetzea.
+[Arduradunkidea (k): Eusko Jaurlaritza, foru-aldundiak] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titular beteranoen ustiategiak gazteei lagatzeko pizgarriak ematea, laguntza ekonomikoen bidez.
+[Arduradunkidea (k): foru-aldundiak] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curriculumak berrikustea eta belaunaldien arteko erreleborako orientazioa sartzea.
+[Arduradunkidea (k): EJ] 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Langile berrientzako laguntza tekniko eta finantzarioko ibilbideak sortzea.
+[Arduradunkidea (k): EJ] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prestakuntza-ibilbideak ustiategien lagatzaile izan daitezkeenentzat. Bertan, ustiategi baten transmisioarekin lotutako hainbat gestiori buruzko informazioa emango zaie (alderdi fiskalak, legalak, NPB, laguntzak...).
+[Arduradunkidea (k): GFA] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landa-eremuetan konektibitatea, etxebizitza, kultura- eta aisialdi-zerbitzuak hobetzea.
+[Arduradunkidea (k): Eusko Jaurlaritza, foru-aldundiak] </t>
   </si>
 </sst>
 </file>
@@ -1483,13 +1699,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:7" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1499,7 +1715,7 @@
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>1</v>
       </c>
@@ -1509,7 +1725,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="6" spans="2:7" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
         <v>2</v>
       </c>
@@ -1519,7 +1735,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>3</v>
       </c>
@@ -1529,7 +1745,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
         <v>4</v>
       </c>
@@ -1539,7 +1755,7 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
@@ -1549,7 +1765,7 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
@@ -1559,7 +1775,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="13" t="s">
         <v>7</v>
       </c>
@@ -1569,7 +1785,7 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13" t="s">
         <v>8</v>
       </c>
@@ -1579,7 +1795,7 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>9</v>
       </c>
@@ -1589,7 +1805,7 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="15" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>10</v>
       </c>
@@ -1599,7 +1815,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="17" spans="2:7" ht="15.4" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
         <v>11</v>
       </c>
@@ -1609,7 +1825,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="19" spans="2:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:7" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
@@ -1621,7 +1837,7 @@
       <c r="F19" s="10"/>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
@@ -1633,7 +1849,7 @@
       <c r="F20" s="10"/>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
@@ -1645,7 +1861,7 @@
       <c r="F21" s="10"/>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
@@ -1657,7 +1873,7 @@
       <c r="F22" s="10"/>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>20</v>
       </c>
@@ -1669,7 +1885,7 @@
       <c r="F23" s="10"/>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
@@ -1681,7 +1897,7 @@
       <c r="F24" s="10"/>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
@@ -1693,7 +1909,7 @@
       <c r="F25" s="10"/>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>26</v>
       </c>
@@ -1735,7 +1951,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="32" customWidth="1"/>
@@ -1745,7 +1961,7 @@
     <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
@@ -1757,7 +1973,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -1783,7 +1999,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="70.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="70.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -1805,27 +2021,30 @@
       <c r="G4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>265</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>42</v>
       </c>
@@ -1833,7 +2052,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
@@ -1847,7 +2066,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>45</v>
       </c>
@@ -1861,7 +2080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
@@ -1875,7 +2094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>51</v>
       </c>
@@ -1889,7 +2108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>54</v>
       </c>
@@ -1903,7 +2122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>57</v>
       </c>
@@ -1917,7 +2136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>60</v>
       </c>
@@ -1931,7 +2150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1945,7 +2164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>66</v>
       </c>
@@ -1970,7 +2189,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
@@ -1978,7 +2197,7 @@
     <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>18</v>
       </c>
@@ -1986,7 +2205,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
@@ -2000,7 +2219,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -2012,7 +2231,7 @@
       </c>
       <c r="D4" s="3"/>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>75</v>
       </c>
@@ -2024,7 +2243,7 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>77</v>
       </c>
@@ -2036,7 +2255,7 @@
       </c>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>80</v>
       </c>
@@ -2048,7 +2267,7 @@
       </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>82</v>
       </c>
@@ -2060,7 +2279,7 @@
       </c>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>84</v>
       </c>
@@ -2083,21 +2302,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:K25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="6" max="6" width="40.140625" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>86</v>
       </c>
@@ -2112,7 +2331,7 @@
       <c r="J1" s="8"/>
       <c r="K1" s="8"/>
     </row>
-    <row r="3" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>87</v>
       </c>
@@ -2147,7 +2366,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="58.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>94</v>
       </c>
@@ -2157,11 +2376,15 @@
       <c r="C4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="E4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>320</v>
+      </c>
       <c r="G4" s="5">
         <v>0</v>
       </c>
@@ -2178,7 +2401,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>100</v>
       </c>
@@ -2188,11 +2411,15 @@
       <c r="C5" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="G5" s="5">
         <v>0</v>
       </c>
@@ -2209,7 +2436,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>104</v>
       </c>
@@ -2219,11 +2446,15 @@
       <c r="C6" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>290</v>
+      </c>
       <c r="E6" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="G6" s="5">
         <v>0</v>
       </c>
@@ -2240,7 +2471,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>108</v>
       </c>
@@ -2250,11 +2481,15 @@
       <c r="C7" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3" t="s">
+        <v>291</v>
+      </c>
       <c r="E7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="G7" s="6">
         <v>365000</v>
       </c>
@@ -2271,7 +2506,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>111</v>
       </c>
@@ -2281,11 +2516,15 @@
       <c r="C8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>292</v>
+      </c>
       <c r="E8" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>316</v>
+      </c>
       <c r="G8" s="6">
         <v>365000</v>
       </c>
@@ -2302,7 +2541,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="43.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>114</v>
       </c>
@@ -2312,11 +2551,15 @@
       <c r="C9" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>315</v>
+      </c>
       <c r="G9" s="6">
         <v>95000</v>
       </c>
@@ -2333,7 +2576,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>118</v>
       </c>
@@ -2343,11 +2586,15 @@
       <c r="C10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="G10" s="6">
         <v>1500000</v>
       </c>
@@ -2364,7 +2611,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>123</v>
       </c>
@@ -2374,11 +2621,15 @@
       <c r="C11" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="G11" s="6">
         <v>800000</v>
       </c>
@@ -2395,7 +2646,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="53" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" ht="53.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>126</v>
       </c>
@@ -2405,11 +2656,15 @@
       <c r="C12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>296</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>323</v>
+      </c>
       <c r="G12" s="5">
         <v>0</v>
       </c>
@@ -2426,7 +2681,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="41" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>131</v>
       </c>
@@ -2436,11 +2691,15 @@
       <c r="C13" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="E13" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="G13" s="6">
         <v>15000</v>
       </c>
@@ -2457,7 +2716,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>134</v>
       </c>
@@ -2467,11 +2726,15 @@
       <c r="C14" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>298</v>
+      </c>
       <c r="E14" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="G14" s="5">
         <v>0</v>
       </c>
@@ -2488,7 +2751,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>137</v>
       </c>
@@ -2498,11 +2761,15 @@
       <c r="C15" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>299</v>
+      </c>
       <c r="E15" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="G15" s="6">
         <v>4570000</v>
       </c>
@@ -2519,7 +2786,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>140</v>
       </c>
@@ -2529,11 +2796,15 @@
       <c r="C16" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>300</v>
+      </c>
       <c r="E16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>326</v>
+      </c>
       <c r="G16" s="6">
         <v>3000000</v>
       </c>
@@ -2550,7 +2821,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>143</v>
       </c>
@@ -2560,11 +2831,15 @@
       <c r="C17" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="E17" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="G17" s="6">
         <v>3800000</v>
       </c>
@@ -2581,7 +2856,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>146</v>
       </c>
@@ -2591,11 +2866,15 @@
       <c r="C18" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="E18" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="G18" s="5">
         <v>0</v>
       </c>
@@ -2612,7 +2891,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>149</v>
       </c>
@@ -2622,11 +2901,15 @@
       <c r="C19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="E19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="G19" s="6">
         <v>9750000</v>
       </c>
@@ -2643,7 +2926,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="43.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>152</v>
       </c>
@@ -2653,11 +2936,15 @@
       <c r="C20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="E20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>327</v>
+      </c>
       <c r="G20" s="5">
         <v>0</v>
       </c>
@@ -2674,7 +2961,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>155</v>
       </c>
@@ -2684,11 +2971,15 @@
       <c r="C21" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>305</v>
+      </c>
       <c r="E21" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>310</v>
+      </c>
       <c r="G21" s="6">
         <v>150000</v>
       </c>
@@ -2705,7 +2996,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>158</v>
       </c>
@@ -2715,11 +3006,15 @@
       <c r="C22" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="3" t="s">
+        <v>159</v>
+      </c>
       <c r="E22" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>309</v>
+      </c>
       <c r="G22" s="6">
         <v>796000</v>
       </c>
@@ -2736,7 +3031,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>161</v>
       </c>
@@ -2746,11 +3041,15 @@
       <c r="C23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>306</v>
+      </c>
       <c r="E23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>328</v>
+      </c>
       <c r="G23" s="5">
         <v>0</v>
       </c>
@@ -2767,7 +3066,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>164</v>
       </c>
@@ -2777,11 +3076,15 @@
       <c r="C24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="E24" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G24" s="5">
         <v>0</v>
       </c>
@@ -2798,7 +3101,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="47" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" ht="47.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>167</v>
       </c>
@@ -2808,11 +3111,15 @@
       <c r="C25" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3" t="s">
+        <v>308</v>
+      </c>
       <c r="E25" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>330</v>
+      </c>
       <c r="G25" s="5">
         <v>0</v>
       </c>
@@ -2841,7 +3148,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -2854,7 +3161,7 @@
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>170</v>
       </c>
@@ -2870,7 +3177,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>171</v>
       </c>
@@ -2908,14 +3215,16 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="79.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="D4" s="4" t="s">
         <v>182</v>
       </c>
@@ -2925,7 +3234,9 @@
       <c r="F4" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3">
@@ -2938,14 +3249,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="100.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="100.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="D5" s="4" t="s">
         <v>182</v>
       </c>
@@ -2955,7 +3268,9 @@
       <c r="F5" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>286</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3">
@@ -2968,14 +3283,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="98" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>268</v>
+      </c>
       <c r="D6" s="4" t="s">
         <v>182</v>
       </c>
@@ -2985,7 +3302,9 @@
       <c r="F6" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="H6" s="3">
         <v>58.4</v>
       </c>
@@ -3002,14 +3321,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>193</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="D7" s="4" t="s">
         <v>182</v>
       </c>
@@ -3019,7 +3340,9 @@
       <c r="F7" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G7" s="3"/>
+      <c r="G7" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4">
@@ -3032,14 +3355,16 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>197</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="D8" s="4" t="s">
         <v>199</v>
       </c>
@@ -3049,7 +3374,9 @@
       <c r="F8" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>283</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3">
@@ -3062,14 +3389,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="80" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>202</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="D9" s="4" t="s">
         <v>199</v>
       </c>
@@ -3079,7 +3408,9 @@
       <c r="F9" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3">
@@ -3092,14 +3423,16 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="97.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="97.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>205</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="D10" s="4" t="s">
         <v>199</v>
       </c>
@@ -3109,7 +3442,9 @@
       <c r="F10" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="G10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3">
@@ -3122,14 +3457,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="59" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="59.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>208</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="D11" s="4" t="s">
         <v>199</v>
       </c>
@@ -3139,7 +3476,9 @@
       <c r="F11" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3">
@@ -3152,14 +3491,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>212</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="D12" s="4" t="s">
         <v>214</v>
       </c>
@@ -3169,7 +3510,9 @@
       <c r="F12" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3">
@@ -3182,14 +3525,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="79.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="79.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>216</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="D13" s="4" t="s">
         <v>214</v>
       </c>
@@ -3199,7 +3544,9 @@
       <c r="F13" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="G13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>278</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3">
@@ -3212,14 +3559,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="98" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" ht="98.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>219</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="D14" s="4" t="s">
         <v>214</v>
       </c>
@@ -3229,7 +3578,9 @@
       <c r="F14" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3">
@@ -3254,7 +3605,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -3262,7 +3613,7 @@
     <col min="4" max="4" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>222</v>
       </c>
@@ -3270,7 +3621,7 @@
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>171</v>
       </c>
@@ -3284,7 +3635,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
@@ -3298,7 +3649,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>193</v>
       </c>
@@ -3312,7 +3663,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>197</v>
       </c>
@@ -3326,7 +3677,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>208</v>
       </c>
@@ -3340,7 +3691,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>216</v>
       </c>
@@ -3365,7 +3716,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -3376,7 +3727,7 @@
     <col min="8" max="8" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22.5" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>231</v>
       </c>
@@ -3388,7 +3739,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>87</v>
       </c>
@@ -3414,7 +3765,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>94</v>
       </c>
@@ -3434,7 +3785,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>100</v>
       </c>
@@ -3454,7 +3805,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>104</v>
       </c>
@@ -3474,7 +3825,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>108</v>
       </c>
@@ -3496,7 +3847,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>111</v>
       </c>
@@ -3518,7 +3869,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="46.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="46.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>114</v>
       </c>
@@ -3538,7 +3889,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>118</v>
       </c>
@@ -3558,7 +3909,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>123</v>
       </c>
@@ -3580,7 +3931,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>126</v>
       </c>
@@ -3600,7 +3951,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="41" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>131</v>
       </c>
@@ -3620,7 +3971,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="73.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" ht="73.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>134</v>
       </c>
@@ -3640,7 +3991,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="59" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="59.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>137</v>
       </c>
@@ -3660,7 +4011,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>140</v>
       </c>
@@ -3680,7 +4031,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>143</v>
       </c>
@@ -3702,7 +4053,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>146</v>
       </c>
@@ -3722,7 +4073,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>149</v>
       </c>
@@ -3742,7 +4093,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>152</v>
       </c>
@@ -3762,7 +4113,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>155</v>
       </c>
@@ -3782,7 +4133,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>158</v>
       </c>
@@ -3802,7 +4153,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>161</v>
       </c>
@@ -3822,7 +4173,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>164</v>
       </c>
@@ -3842,7 +4193,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="64.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" ht="64.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>167</v>
       </c>
@@ -3862,7 +4213,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>123</v>
       </c>
@@ -3884,7 +4235,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>131</v>
       </c>
@@ -3904,7 +4255,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
@@ -3924,7 +4275,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="88.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" ht="88.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>158</v>
       </c>
@@ -3944,7 +4295,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="91.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" ht="91.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>164</v>
       </c>
